--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>79168</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R25" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R26" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>79196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R25" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B26" t="n">
-        <v>79184</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R26" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>79196</v>
+        <v>78133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R25" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>79196</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R26" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B25" t="n">
-        <v>78155</v>
+        <v>79222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R25" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B26" t="n">
-        <v>79218</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R26" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>79222</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R25" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R26" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3410,7 +3410,7 @@
         <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>79237</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R25" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B26" t="n">
-        <v>79235</v>
+        <v>78173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R26" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3407,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361358</v>
+        <v>113361370</v>
       </c>
       <c r="B25" t="n">
-        <v>79237</v>
+        <v>78201</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577486</v>
+        <v>577439</v>
       </c>
       <c r="R25" t="n">
-        <v>7078499</v>
+        <v>7078556</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361370</v>
+        <v>113361358</v>
       </c>
       <c r="B26" t="n">
-        <v>78173</v>
+        <v>79265</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577439</v>
+        <v>577486</v>
       </c>
       <c r="R26" t="n">
-        <v>7078556</v>
+        <v>7078499</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119872160</v>
+        <v>119870289</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,34 +4353,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577587</v>
+        <v>577682</v>
       </c>
       <c r="R34" t="n">
-        <v>7078423</v>
+        <v>7078391</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4407,12 +4407,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,22 +4427,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870289</v>
+        <v>119872160</v>
       </c>
       <c r="B35" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577682</v>
+        <v>577587</v>
       </c>
       <c r="R35" t="n">
-        <v>7078391</v>
+        <v>7078423</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,12 +4529,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871262</v>
+        <v>119871879</v>
       </c>
       <c r="B27" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577628</v>
+        <v>577593</v>
       </c>
       <c r="R27" t="n">
-        <v>7078417</v>
+        <v>7078428</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119870350</v>
+        <v>119873387</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577686</v>
+        <v>577493</v>
       </c>
       <c r="R28" t="n">
-        <v>7078384</v>
+        <v>7078500</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871466</v>
+        <v>119871885</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,25 +3835,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577614</v>
+        <v>577588</v>
       </c>
       <c r="R29" t="n">
-        <v>7078408</v>
+        <v>7078435</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119870410</v>
+        <v>119871262</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,25 +3937,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577692</v>
+        <v>577628</v>
       </c>
       <c r="R30" t="n">
-        <v>7078377</v>
+        <v>7078417</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871879</v>
+        <v>119870519</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>90905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,41 +4039,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577593</v>
+        <v>577693</v>
       </c>
       <c r="R31" t="n">
-        <v>7078428</v>
+        <v>7078382</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4117,22 +4117,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871836</v>
+        <v>119870350</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,45 +4141,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577614</v>
+        <v>577686</v>
       </c>
       <c r="R32" t="n">
-        <v>7078416</v>
+        <v>7078384</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4203,12 +4199,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119870519</v>
+        <v>119870410</v>
       </c>
       <c r="B33" t="n">
-        <v>90905</v>
+        <v>90527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,41 +4243,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577693</v>
+        <v>577692</v>
       </c>
       <c r="R33" t="n">
-        <v>7078382</v>
+        <v>7078377</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,12 +4301,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,22 +4321,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119870289</v>
+        <v>119873378</v>
       </c>
       <c r="B34" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4349,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4373,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577682</v>
+        <v>577458</v>
       </c>
       <c r="R34" t="n">
-        <v>7078391</v>
+        <v>7078517</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4407,12 +4403,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,19 +4423,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119872160</v>
+        <v>119871949</v>
       </c>
       <c r="B35" t="n">
         <v>78526</v>
@@ -4475,17 +4471,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577587</v>
+        <v>577573</v>
       </c>
       <c r="R35" t="n">
-        <v>7078423</v>
+        <v>7078427</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4529,22 +4525,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871885</v>
+        <v>119871466</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4553,25 +4549,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4581,10 +4577,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R36" t="n">
-        <v>7078435</v>
+        <v>7078408</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4643,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873387</v>
+        <v>119872160</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4659,34 +4655,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577493</v>
+        <v>577587</v>
       </c>
       <c r="R37" t="n">
-        <v>7078500</v>
+        <v>7078423</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4733,22 +4729,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871949</v>
+        <v>119871836</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,38 +4753,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577573</v>
+        <v>577614</v>
       </c>
       <c r="R38" t="n">
-        <v>7078427</v>
+        <v>7078416</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119873378</v>
+        <v>119870289</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4863,21 +4863,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577458</v>
+        <v>577682</v>
       </c>
       <c r="R39" t="n">
-        <v>7078517</v>
+        <v>7078391</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3721,10 +3721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119873387</v>
+        <v>119870350</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577493</v>
+        <v>577686</v>
       </c>
       <c r="R28" t="n">
-        <v>7078500</v>
+        <v>7078384</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871885</v>
+        <v>119872160</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,25 +3835,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577588</v>
+        <v>577587</v>
       </c>
       <c r="R29" t="n">
-        <v>7078435</v>
+        <v>7078423</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871262</v>
+        <v>119871466</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577628</v>
+        <v>577614</v>
       </c>
       <c r="R30" t="n">
-        <v>7078417</v>
+        <v>7078408</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119870519</v>
+        <v>119871836</v>
       </c>
       <c r="B31" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,34 +4043,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577693</v>
+        <v>577614</v>
       </c>
       <c r="R31" t="n">
-        <v>7078382</v>
+        <v>7078416</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,12 +4101,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119870350</v>
+        <v>119871949</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,21 +4149,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4169,13 +4173,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577686</v>
+        <v>577573</v>
       </c>
       <c r="R32" t="n">
-        <v>7078384</v>
+        <v>7078427</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4199,12 +4203,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119870410</v>
+        <v>119873378</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,38 +4247,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577692</v>
+        <v>577458</v>
       </c>
       <c r="R33" t="n">
-        <v>7078377</v>
+        <v>7078517</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4333,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119873378</v>
+        <v>119870519</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>90905</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4345,25 +4349,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4373,13 +4377,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577458</v>
+        <v>577693</v>
       </c>
       <c r="R34" t="n">
-        <v>7078517</v>
+        <v>7078382</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4403,12 +4407,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4423,22 +4427,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119871949</v>
+        <v>119871262</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,37 +4455,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577573</v>
+        <v>577628</v>
       </c>
       <c r="R35" t="n">
-        <v>7078427</v>
+        <v>7078417</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4525,22 +4529,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871466</v>
+        <v>119870410</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4549,25 +4553,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4577,10 +4581,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577614</v>
+        <v>577692</v>
       </c>
       <c r="R36" t="n">
-        <v>7078408</v>
+        <v>7078377</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4639,10 +4643,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119872160</v>
+        <v>119871885</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,25 +4655,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4679,10 +4683,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577587</v>
+        <v>577588</v>
       </c>
       <c r="R37" t="n">
-        <v>7078423</v>
+        <v>7078435</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4741,10 +4745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871836</v>
+        <v>119873387</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,45 +4757,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577614</v>
+        <v>577493</v>
       </c>
       <c r="R38" t="n">
-        <v>7078416</v>
+        <v>7078500</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -4745,10 +4745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873387</v>
+        <v>119870289</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4761,21 +4761,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577493</v>
+        <v>577682</v>
       </c>
       <c r="R38" t="n">
-        <v>7078500</v>
+        <v>7078391</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,10 +4847,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119870289</v>
+        <v>119873387</v>
       </c>
       <c r="B39" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4863,21 +4863,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577682</v>
+        <v>577493</v>
       </c>
       <c r="R39" t="n">
-        <v>7078391</v>
+        <v>7078500</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871879</v>
+        <v>119871949</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3631,41 +3631,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577593</v>
+        <v>577573</v>
       </c>
       <c r="R27" t="n">
-        <v>7078428</v>
+        <v>7078427</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3709,22 +3709,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119870350</v>
+        <v>119870519</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577686</v>
+        <v>577693</v>
       </c>
       <c r="R28" t="n">
-        <v>7078384</v>
+        <v>7078382</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119872160</v>
+        <v>119871262</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577587</v>
+        <v>577628</v>
       </c>
       <c r="R29" t="n">
-        <v>7078423</v>
+        <v>7078417</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871466</v>
+        <v>119871885</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,25 +3937,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577614</v>
+        <v>577588</v>
       </c>
       <c r="R30" t="n">
-        <v>7078408</v>
+        <v>7078435</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871836</v>
+        <v>119873387</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,45 +4039,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577614</v>
+        <v>577493</v>
       </c>
       <c r="R31" t="n">
-        <v>7078416</v>
+        <v>7078500</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4133,10 +4129,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871949</v>
+        <v>119871836</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,38 +4141,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577573</v>
+        <v>577614</v>
       </c>
       <c r="R32" t="n">
-        <v>7078427</v>
+        <v>7078416</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119873378</v>
+        <v>119870410</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,38 +4247,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577458</v>
+        <v>577692</v>
       </c>
       <c r="R33" t="n">
-        <v>7078517</v>
+        <v>7078377</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119870519</v>
+        <v>119872160</v>
       </c>
       <c r="B34" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,41 +4349,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577693</v>
+        <v>577587</v>
       </c>
       <c r="R34" t="n">
-        <v>7078382</v>
+        <v>7078423</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4407,12 +4407,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,19 +4427,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119871262</v>
+        <v>119870350</v>
       </c>
       <c r="B35" t="n">
         <v>90562</v>
@@ -4475,14 +4475,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577628</v>
+        <v>577686</v>
       </c>
       <c r="R35" t="n">
-        <v>7078417</v>
+        <v>7078384</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,22 +4529,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119870410</v>
+        <v>119873378</v>
       </c>
       <c r="B36" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4553,38 +4553,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577692</v>
+        <v>577458</v>
       </c>
       <c r="R36" t="n">
-        <v>7078377</v>
+        <v>7078517</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871885</v>
+        <v>119870289</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,38 +4655,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577588</v>
+        <v>577682</v>
       </c>
       <c r="R37" t="n">
-        <v>7078435</v>
+        <v>7078391</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,22 +4733,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119870289</v>
+        <v>119871879</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,38 +4757,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577682</v>
+        <v>577593</v>
       </c>
       <c r="R38" t="n">
-        <v>7078391</v>
+        <v>7078428</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,22 +4835,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119873387</v>
+        <v>119871466</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577493</v>
+        <v>577614</v>
       </c>
       <c r="R39" t="n">
-        <v>7078500</v>
+        <v>7078408</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871949</v>
+        <v>119871879</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3631,41 +3631,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577573</v>
+        <v>577593</v>
       </c>
       <c r="R27" t="n">
-        <v>7078427</v>
+        <v>7078428</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3709,22 +3709,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119870519</v>
+        <v>119872160</v>
       </c>
       <c r="B28" t="n">
-        <v>90905</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,41 +3733,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577693</v>
+        <v>577587</v>
       </c>
       <c r="R28" t="n">
-        <v>7078382</v>
+        <v>7078423</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,22 +3811,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871262</v>
+        <v>119873378</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,34 +3839,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577628</v>
+        <v>577458</v>
       </c>
       <c r="R29" t="n">
-        <v>7078417</v>
+        <v>7078517</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871885</v>
+        <v>119870350</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,38 +3937,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577588</v>
+        <v>577686</v>
       </c>
       <c r="R30" t="n">
-        <v>7078435</v>
+        <v>7078384</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4015,22 +4015,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119873387</v>
+        <v>119870519</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>90923</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,25 +4039,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4067,13 +4067,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577493</v>
+        <v>577693</v>
       </c>
       <c r="R31" t="n">
-        <v>7078500</v>
+        <v>7078382</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871836</v>
+        <v>119870410</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,45 +4141,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577614</v>
+        <v>577692</v>
       </c>
       <c r="R32" t="n">
-        <v>7078416</v>
+        <v>7078377</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4223,22 +4219,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119870410</v>
+        <v>119871885</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,25 +4243,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577692</v>
+        <v>577588</v>
       </c>
       <c r="R33" t="n">
-        <v>7078377</v>
+        <v>7078435</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4337,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119872160</v>
+        <v>119871262</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4349,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4373,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577587</v>
+        <v>577628</v>
       </c>
       <c r="R34" t="n">
-        <v>7078423</v>
+        <v>7078417</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4439,10 +4435,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870350</v>
+        <v>119871836</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,41 +4447,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577686</v>
+        <v>577614</v>
       </c>
       <c r="R35" t="n">
-        <v>7078384</v>
+        <v>7078416</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,10 +4541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119873378</v>
+        <v>119870289</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577458</v>
+        <v>577682</v>
       </c>
       <c r="R36" t="n">
-        <v>7078517</v>
+        <v>7078391</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,22 +4631,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119870289</v>
+        <v>119871466</v>
       </c>
       <c r="B37" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577682</v>
+        <v>577614</v>
       </c>
       <c r="R37" t="n">
-        <v>7078391</v>
+        <v>7078408</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,22 +4733,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871879</v>
+        <v>119873387</v>
       </c>
       <c r="B38" t="n">
-        <v>90527</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,38 +4757,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577593</v>
+        <v>577493</v>
       </c>
       <c r="R38" t="n">
-        <v>7078428</v>
+        <v>7078500</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4835,22 +4835,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871466</v>
+        <v>119871949</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4883,17 +4883,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577614</v>
+        <v>577573</v>
       </c>
       <c r="R39" t="n">
-        <v>7078408</v>
+        <v>7078427</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871879</v>
+        <v>119871949</v>
       </c>
       <c r="B27" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3631,41 +3631,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577593</v>
+        <v>577573</v>
       </c>
       <c r="R27" t="n">
-        <v>7078428</v>
+        <v>7078427</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3709,22 +3709,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119872160</v>
+        <v>119871879</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577587</v>
+        <v>577593</v>
       </c>
       <c r="R28" t="n">
-        <v>7078423</v>
+        <v>7078428</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873378</v>
+        <v>119870289</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577458</v>
+        <v>577682</v>
       </c>
       <c r="R29" t="n">
-        <v>7078517</v>
+        <v>7078391</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,22 +3913,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119870350</v>
+        <v>119870410</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,38 +3937,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577686</v>
+        <v>577692</v>
       </c>
       <c r="R30" t="n">
-        <v>7078384</v>
+        <v>7078377</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4015,22 +4015,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119870519</v>
+        <v>119871836</v>
       </c>
       <c r="B31" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4043,34 +4043,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577693</v>
+        <v>577614</v>
       </c>
       <c r="R31" t="n">
-        <v>7078382</v>
+        <v>7078416</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,12 +4101,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119870410</v>
+        <v>119873387</v>
       </c>
       <c r="B32" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,38 +4145,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577692</v>
+        <v>577493</v>
       </c>
       <c r="R32" t="n">
-        <v>7078377</v>
+        <v>7078500</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4219,12 +4223,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4333,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871262</v>
+        <v>119873378</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,34 +4353,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577628</v>
+        <v>577458</v>
       </c>
       <c r="R34" t="n">
-        <v>7078417</v>
+        <v>7078517</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4435,10 +4439,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119871836</v>
+        <v>119870350</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4447,45 +4451,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577614</v>
+        <v>577686</v>
       </c>
       <c r="R35" t="n">
-        <v>7078416</v>
+        <v>7078384</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,10 +4541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119870289</v>
+        <v>119872160</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4557,34 +4557,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577682</v>
+        <v>577587</v>
       </c>
       <c r="R36" t="n">
-        <v>7078391</v>
+        <v>7078423</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,22 +4631,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871466</v>
+        <v>119870519</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,41 +4655,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577614</v>
+        <v>577693</v>
       </c>
       <c r="R37" t="n">
-        <v>7078408</v>
+        <v>7078382</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,22 +4733,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873387</v>
+        <v>119871262</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4761,34 +4761,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577493</v>
+        <v>577628</v>
       </c>
       <c r="R38" t="n">
-        <v>7078500</v>
+        <v>7078417</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4835,19 +4835,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871949</v>
+        <v>119871466</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -4883,17 +4883,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577573</v>
+        <v>577614</v>
       </c>
       <c r="R39" t="n">
-        <v>7078427</v>
+        <v>7078408</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871949</v>
+        <v>119870289</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3635,21 +3635,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3659,13 +3659,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577573</v>
+        <v>577682</v>
       </c>
       <c r="R27" t="n">
-        <v>7078427</v>
+        <v>7078391</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871879</v>
+        <v>119871885</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577593</v>
+        <v>577588</v>
       </c>
       <c r="R28" t="n">
-        <v>7078428</v>
+        <v>7078435</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119870289</v>
+        <v>119873387</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577682</v>
+        <v>577493</v>
       </c>
       <c r="R29" t="n">
-        <v>7078391</v>
+        <v>7078500</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119870410</v>
+        <v>119872160</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,25 +3937,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577692</v>
+        <v>577587</v>
       </c>
       <c r="R30" t="n">
-        <v>7078377</v>
+        <v>7078423</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871836</v>
+        <v>119871262</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,45 +4039,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577614</v>
+        <v>577628</v>
       </c>
       <c r="R31" t="n">
-        <v>7078416</v>
+        <v>7078417</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4121,22 +4117,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873387</v>
+        <v>119871466</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4149,34 +4145,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577493</v>
+        <v>577614</v>
       </c>
       <c r="R32" t="n">
-        <v>7078500</v>
+        <v>7078408</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4223,22 +4219,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119871885</v>
+        <v>119871949</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,41 +4243,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577588</v>
+        <v>577573</v>
       </c>
       <c r="R33" t="n">
-        <v>7078435</v>
+        <v>7078427</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4325,22 +4321,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119873378</v>
+        <v>119870350</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4349,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4373,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577458</v>
+        <v>577686</v>
       </c>
       <c r="R34" t="n">
-        <v>7078517</v>
+        <v>7078384</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4407,12 +4403,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,22 +4423,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870350</v>
+        <v>119870410</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,38 +4447,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577686</v>
+        <v>577692</v>
       </c>
       <c r="R35" t="n">
-        <v>7078384</v>
+        <v>7078377</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4509,12 +4505,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,22 +4525,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119872160</v>
+        <v>119871836</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4553,41 +4549,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577587</v>
+        <v>577614</v>
       </c>
       <c r="R36" t="n">
-        <v>7078423</v>
+        <v>7078416</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4631,22 +4631,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119870519</v>
+        <v>119873378</v>
       </c>
       <c r="B37" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4655,25 +4655,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577693</v>
+        <v>577458</v>
       </c>
       <c r="R37" t="n">
-        <v>7078382</v>
+        <v>7078517</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,22 +4733,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871262</v>
+        <v>119871879</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,25 +4757,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577628</v>
+        <v>577593</v>
       </c>
       <c r="R38" t="n">
-        <v>7078417</v>
+        <v>7078428</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871466</v>
+        <v>119870519</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,41 +4859,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577614</v>
+        <v>577693</v>
       </c>
       <c r="R39" t="n">
-        <v>7078408</v>
+        <v>7078382</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119870289</v>
+        <v>119871879</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3631,38 +3631,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577682</v>
+        <v>577593</v>
       </c>
       <c r="R27" t="n">
-        <v>7078391</v>
+        <v>7078428</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871885</v>
+        <v>119871466</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R28" t="n">
-        <v>7078435</v>
+        <v>7078408</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873387</v>
+        <v>119870519</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90923</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,25 +3835,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577493</v>
+        <v>577693</v>
       </c>
       <c r="R29" t="n">
-        <v>7078500</v>
+        <v>7078382</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119872160</v>
+        <v>119870410</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,25 +3937,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577587</v>
+        <v>577692</v>
       </c>
       <c r="R30" t="n">
-        <v>7078423</v>
+        <v>7078377</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,10 +4027,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871262</v>
+        <v>119871885</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4039,25 +4039,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577628</v>
+        <v>577588</v>
       </c>
       <c r="R31" t="n">
-        <v>7078417</v>
+        <v>7078435</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871466</v>
+        <v>119872160</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577614</v>
+        <v>577587</v>
       </c>
       <c r="R32" t="n">
-        <v>7078408</v>
+        <v>7078423</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119870350</v>
+        <v>119871262</v>
       </c>
       <c r="B34" t="n">
         <v>90580</v>
@@ -4369,14 +4369,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577686</v>
+        <v>577628</v>
       </c>
       <c r="R34" t="n">
-        <v>7078384</v>
+        <v>7078417</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4403,12 +4403,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4423,22 +4423,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870410</v>
+        <v>119870289</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4447,38 +4447,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577692</v>
+        <v>577682</v>
       </c>
       <c r="R35" t="n">
-        <v>7078377</v>
+        <v>7078391</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4525,12 +4525,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871879</v>
+        <v>119870350</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,38 +4757,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577593</v>
+        <v>577686</v>
       </c>
       <c r="R38" t="n">
-        <v>7078428</v>
+        <v>7078384</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,22 +4835,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119870519</v>
+        <v>119873387</v>
       </c>
       <c r="B39" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,25 +4859,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577693</v>
+        <v>577493</v>
       </c>
       <c r="R39" t="n">
-        <v>7078382</v>
+        <v>7078500</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -3619,7 +3619,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871879</v>
+        <v>119870410</v>
       </c>
       <c r="B27" t="n">
         <v>90545</v>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577593</v>
+        <v>577692</v>
       </c>
       <c r="R27" t="n">
-        <v>7078428</v>
+        <v>7078377</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871466</v>
+        <v>119871879</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577614</v>
+        <v>577593</v>
       </c>
       <c r="R28" t="n">
-        <v>7078408</v>
+        <v>7078428</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119870519</v>
+        <v>119870289</v>
       </c>
       <c r="B29" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,25 +3835,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577693</v>
+        <v>577682</v>
       </c>
       <c r="R29" t="n">
-        <v>7078382</v>
+        <v>7078391</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119870410</v>
+        <v>119873378</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,38 +3937,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577692</v>
+        <v>577458</v>
       </c>
       <c r="R30" t="n">
-        <v>7078377</v>
+        <v>7078517</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871885</v>
+        <v>119871836</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4060,20 +4060,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R31" t="n">
-        <v>7078435</v>
+        <v>7078416</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4117,22 +4121,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119872160</v>
+        <v>119871885</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,25 +4145,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4169,10 +4173,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577587</v>
+        <v>577588</v>
       </c>
       <c r="R32" t="n">
-        <v>7078423</v>
+        <v>7078435</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4231,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119871949</v>
+        <v>119870350</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,21 +4251,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,13 +4275,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577573</v>
+        <v>577686</v>
       </c>
       <c r="R33" t="n">
-        <v>7078427</v>
+        <v>7078384</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4301,12 +4305,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4435,10 +4439,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870289</v>
+        <v>119873387</v>
       </c>
       <c r="B35" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,21 +4455,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,10 +4479,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577682</v>
+        <v>577493</v>
       </c>
       <c r="R35" t="n">
-        <v>7078391</v>
+        <v>7078500</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4505,12 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,10 +4541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871836</v>
+        <v>119870519</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4553,38 +4557,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577614</v>
+        <v>577693</v>
       </c>
       <c r="R36" t="n">
-        <v>7078416</v>
+        <v>7078382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,10 +4643,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873378</v>
+        <v>119871949</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4659,21 +4659,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577458</v>
+        <v>577573</v>
       </c>
       <c r="R37" t="n">
-        <v>7078517</v>
+        <v>7078427</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4733,22 +4733,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119870350</v>
+        <v>119871466</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4761,34 +4761,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577686</v>
+        <v>577614</v>
       </c>
       <c r="R38" t="n">
-        <v>7078384</v>
+        <v>7078408</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,22 +4835,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119873387</v>
+        <v>119872160</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577493</v>
+        <v>577587</v>
       </c>
       <c r="R39" t="n">
-        <v>7078500</v>
+        <v>7078423</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4937,12 +4937,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102368370</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577645.1015351556</v>
+        <v>577645</v>
       </c>
       <c r="R2" t="n">
-        <v>7078431.024434575</v>
+        <v>7078431</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102368364</v>
+        <v>119870289</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577632.7685316374</v>
+        <v>577682</v>
       </c>
       <c r="R3" t="n">
-        <v>7078464.732305993</v>
+        <v>7078391</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,70 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102368371</v>
+        <v>102368362</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577647.6610734588</v>
+        <v>577646</v>
       </c>
       <c r="R4" t="n">
-        <v>7078452.732191161</v>
+        <v>7078442</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,28 +937,17 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102368383</v>
+        <v>102368364</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577365.9901920597</v>
+        <v>577633</v>
       </c>
       <c r="R5" t="n">
-        <v>7078701.086868675</v>
+        <v>7078465</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,19 +1034,9 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,69 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102368234</v>
+        <v>102368365</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577674.7778443468</v>
+        <v>577622</v>
       </c>
       <c r="R6" t="n">
-        <v>7078447.21848609</v>
+        <v>7078481</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,34 +1142,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102368374</v>
+        <v>113360892</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,37 +1171,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577671.1216073042</v>
+        <v>577629</v>
       </c>
       <c r="R7" t="n">
-        <v>7078416.20726666</v>
+        <v>7078378</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,22 +1228,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,33 +1242,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102368373</v>
+        <v>119870350</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,34 +1272,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577619.524225657</v>
+        <v>577686</v>
       </c>
       <c r="R8" t="n">
-        <v>7078481.632074536</v>
+        <v>7078384</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1443,22 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,85 +1346,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102368143</v>
+        <v>119871262</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backe (63.8246, 16.5768), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577602.2895731817</v>
+        <v>577628</v>
       </c>
       <c r="R9" t="n">
-        <v>7078427.316140057</v>
+        <v>7078417</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,27 +1423,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,34 +1437,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac, Michaela Ehmann</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102368362</v>
+        <v>119871920</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,14 +1486,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577646.1548365084</v>
+        <v>577561</v>
       </c>
       <c r="R10" t="n">
-        <v>7078442.093595183</v>
+        <v>7078431</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,22 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,27 +1540,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102368375</v>
+        <v>119872658</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,34 +1563,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577617.0517877815</v>
+        <v>577509</v>
       </c>
       <c r="R11" t="n">
-        <v>7078456.392927467</v>
+        <v>7078448</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1805,22 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,65 +1637,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102368377</v>
+        <v>119870519</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577531.6369373385</v>
+        <v>577693</v>
       </c>
       <c r="R12" t="n">
-        <v>7078476.369538852</v>
+        <v>7078382</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,22 +1714,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,49 +1734,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102368365</v>
+        <v>102368361</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577622.6511469858</v>
+        <v>577516</v>
       </c>
       <c r="R13" t="n">
-        <v>7078480.384188105</v>
+        <v>7078464</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2032,19 +1814,9 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,69 +1843,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102368181</v>
+        <v>119870410</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577672.278575292</v>
+        <v>577692</v>
       </c>
       <c r="R14" t="n">
-        <v>7078405.192653979</v>
+        <v>7078377</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,22 +1908,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,7 +1922,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2200,50 +1940,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102368366</v>
+        <v>119871879</v>
       </c>
       <c r="B15" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577620.9589300179</v>
+        <v>577593</v>
       </c>
       <c r="R15" t="n">
-        <v>7078441.470889287</v>
+        <v>7078428</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2270,22 +2005,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,70 +2025,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102368372</v>
+        <v>119873251</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577645.5929533616</v>
+        <v>577491</v>
       </c>
       <c r="R16" t="n">
-        <v>7078482.718072332</v>
+        <v>7078459</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2390,22 +2102,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,34 +2116,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102862765</v>
+        <v>102368373</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,53 +2145,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577539.0465641895</v>
+        <v>577619</v>
       </c>
       <c r="R17" t="n">
-        <v>7078588.305251198</v>
+        <v>7078481</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,22 +2199,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,34 +2213,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102862799</v>
+        <v>102368374</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,53 +2242,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tägsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577531.9961524863</v>
+        <v>577671</v>
       </c>
       <c r="R18" t="n">
-        <v>7078587.247807395</v>
+        <v>7078416</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2648,22 +2296,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,34 +2310,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102862723</v>
+        <v>102368375</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,53 +2339,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577554.6199639272</v>
+        <v>577617</v>
       </c>
       <c r="R19" t="n">
-        <v>7078566.604507273</v>
+        <v>7078457</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,22 +2393,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2801,75 +2407,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103288957</v>
+        <v>102368376</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577470.3168970675</v>
+        <v>577594</v>
       </c>
       <c r="R20" t="n">
-        <v>7078505.776735188</v>
+        <v>7078513</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2893,22 +2490,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,79 +2504,66 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103288904</v>
+        <v>102368377</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577487.1247096199</v>
+        <v>577532</v>
       </c>
       <c r="R21" t="n">
-        <v>7078505.74960106</v>
+        <v>7078477</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3013,22 +2587,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,34 +2601,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105310353</v>
+        <v>102368378</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,21 +2630,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3096,13 +2654,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577622.0393539499</v>
+        <v>577391</v>
       </c>
       <c r="R22" t="n">
-        <v>7078433.546543271</v>
+        <v>7078542</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3126,22 +2684,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,36 +2700,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105310352</v>
+        <v>119871466</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3189,37 +2727,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577648.152130311</v>
+        <v>577614</v>
       </c>
       <c r="R23" t="n">
-        <v>7078432.866743682</v>
+        <v>7078408</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,22 +2781,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,36 +2797,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105310351</v>
+        <v>119871910</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3306,37 +2824,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577577.6019654577</v>
+        <v>577581</v>
       </c>
       <c r="R24" t="n">
-        <v>7078459.835606844</v>
+        <v>7078410</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3360,22 +2878,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3386,40 +2894,30 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113361370</v>
+        <v>119871949</v>
       </c>
       <c r="B25" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3441,22 +2939,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577440</v>
+        <v>577573</v>
       </c>
       <c r="R25" t="n">
-        <v>7078556</v>
+        <v>7078427</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3480,12 +2975,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,75 +2989,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113361358</v>
+        <v>119872160</v>
       </c>
       <c r="B26" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577486</v>
+        <v>577587</v>
       </c>
       <c r="R26" t="n">
-        <v>7078499</v>
+        <v>7078423</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3586,12 +3072,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3600,7 +3086,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3619,53 +3104,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119870410</v>
+        <v>132083264</v>
       </c>
       <c r="B27" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577692</v>
+        <v>577629</v>
       </c>
       <c r="R27" t="n">
-        <v>7078377</v>
+        <v>7078378</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3689,12 +3169,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,53 +3201,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871879</v>
+        <v>103288904</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577593</v>
+        <v>577488</v>
       </c>
       <c r="R28" t="n">
-        <v>7078428</v>
+        <v>7078506</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3791,12 +3273,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3805,6 +3287,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3823,15 +3306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119870289</v>
+        <v>103288957</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,37 +3317,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577682</v>
+        <v>577470</v>
       </c>
       <c r="R29" t="n">
-        <v>7078391</v>
+        <v>7078506</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,12 +3374,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,33 +3388,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119873378</v>
+        <v>113361143</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,19 +3436,22 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577458</v>
+        <v>577603</v>
       </c>
       <c r="R30" t="n">
-        <v>7078517</v>
+        <v>7078386</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3995,12 +3475,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,6 +3489,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4027,57 +3508,51 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871836</v>
+        <v>113361358</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577614</v>
+        <v>577486</v>
       </c>
       <c r="R31" t="n">
-        <v>7078416</v>
+        <v>7078499</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4101,12 +3576,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,68 +3590,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871885</v>
+        <v>119871553</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577588</v>
+        <v>577606</v>
       </c>
       <c r="R32" t="n">
-        <v>7078435</v>
+        <v>7078395</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4203,12 +3674,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4223,27 +3694,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119870350</v>
+        <v>119873378</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4251,21 +3717,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4275,10 +3741,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577686</v>
+        <v>577458</v>
       </c>
       <c r="R33" t="n">
-        <v>7078384</v>
+        <v>7078517</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4305,12 +3771,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,27 +3791,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871262</v>
+        <v>119873387</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,34 +3814,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577628</v>
+        <v>577493</v>
       </c>
       <c r="R34" t="n">
-        <v>7078417</v>
+        <v>7078500</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4427,27 +3888,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873387</v>
+        <v>119873511</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,10 +3935,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577493</v>
+        <v>577445</v>
       </c>
       <c r="R35" t="n">
-        <v>7078500</v>
+        <v>7078496</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4541,50 +3997,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119870519</v>
+        <v>133340463</v>
       </c>
       <c r="B36" t="n">
-        <v>90923</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577693</v>
+        <v>577604</v>
       </c>
       <c r="R36" t="n">
-        <v>7078382</v>
+        <v>7078411</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4611,12 +4062,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4631,49 +4082,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871949</v>
+        <v>119873574</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4683,13 +4129,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577573</v>
+        <v>577449</v>
       </c>
       <c r="R37" t="n">
-        <v>7078427</v>
+        <v>7078503</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4733,27 +4179,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871466</v>
+        <v>132086547</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4761,34 +4202,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577614</v>
+        <v>577546</v>
       </c>
       <c r="R38" t="n">
-        <v>7078408</v>
+        <v>7078489</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4815,12 +4266,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,15 +4303,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119872160</v>
+        <v>132086668</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4863,37 +4314,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577587</v>
+        <v>577545</v>
       </c>
       <c r="R39" t="n">
-        <v>7078423</v>
+        <v>7078493</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,12 +4378,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färsk ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,10 +4415,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132087499</v>
+        <v>132086694</v>
       </c>
       <c r="B40" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4990,14 +4456,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577562</v>
+        <v>577537</v>
       </c>
       <c r="R40" t="n">
-        <v>7078474</v>
+        <v>7078507</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5034,7 +4500,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färsk ringhack</t>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,10 +4527,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132086694</v>
+        <v>132086911</v>
       </c>
       <c r="B41" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,13 +4572,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577537</v>
+        <v>577521</v>
       </c>
       <c r="R41" t="n">
-        <v>7078507</v>
+        <v>7078509</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5173,10 +4639,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132086668</v>
+        <v>132086988</v>
       </c>
       <c r="B42" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,10 +4684,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577545</v>
+        <v>577523</v>
       </c>
       <c r="R42" t="n">
-        <v>7078493</v>
+        <v>7078521</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5258,7 +4724,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk ringhack</t>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132087575</v>
+        <v>132087060</v>
       </c>
       <c r="B43" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5313,7 +4779,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -5326,14 +4796,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577569</v>
+        <v>577511</v>
       </c>
       <c r="R43" t="n">
-        <v>7078456</v>
+        <v>7078536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5370,7 +4840,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>FÄRSK ringhack</t>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5400,7 +4870,7 @@
         <v>132087340</v>
       </c>
       <c r="B44" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5509,10 +4979,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132086547</v>
+        <v>132087456</v>
       </c>
       <c r="B45" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5550,17 +5020,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577546</v>
+        <v>577555</v>
       </c>
       <c r="R45" t="n">
-        <v>7078489</v>
+        <v>7078481</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5621,10 +5091,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132087456</v>
+        <v>132087499</v>
       </c>
       <c r="B46" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5666,10 +5136,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577555</v>
+        <v>577562</v>
       </c>
       <c r="R46" t="n">
-        <v>7078481</v>
+        <v>7078474</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5706,7 +5176,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färsk Ringhack</t>
+          <t>Färsk ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5733,10 +5203,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132086911</v>
+        <v>132087575</v>
       </c>
       <c r="B47" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,17 +5244,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577521</v>
+        <v>577569</v>
       </c>
       <c r="R47" t="n">
-        <v>7078509</v>
+        <v>7078456</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5818,7 +5288,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färsk Ringhack</t>
+          <t>FÄRSK ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,10 +5315,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132087060</v>
+        <v>133675585</v>
       </c>
       <c r="B48" t="n">
-        <v>57954</v>
+        <v>58231</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5856,51 +5326,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>102980</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577511</v>
+        <v>577697</v>
       </c>
       <c r="R48" t="n">
-        <v>7078536</v>
+        <v>7078402</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5924,17 +5380,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färsk Ringhack</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5412,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132086988</v>
+        <v>102368366</v>
       </c>
       <c r="B49" t="n">
-        <v>57954</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5972,47 +5423,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577523</v>
+        <v>577621</v>
       </c>
       <c r="R49" t="n">
-        <v>7078521</v>
+        <v>7078442</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6036,17 +5477,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färsk Ringhack</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6061,69 +5497,68 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133378044</v>
+        <v>119873589</v>
       </c>
       <c r="B50" t="n">
-        <v>99178</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577359</v>
+        <v>577449</v>
       </c>
       <c r="R50" t="n">
-        <v>7078691</v>
+        <v>7078490</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6147,12 +5582,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6167,15 +5602,3176 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128716003</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>577604</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Michaela Ehmann</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Michaela Ehmann</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132084029</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>togsjön, togsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>577542</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7078438</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>102368384</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>577494</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7078469</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>102368098</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Backe (63.8256, 16.5761), Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>577565</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7078538</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>102368143</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Backe (63.8246, 16.5768), Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>577602</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7078427</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>102368181</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>577673</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7078406</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>102368234</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>577675</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7078447</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>102368371</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>577648</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7078453</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>102368372</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>577645</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078483</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>102862533</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>577613</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078506</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>102862973</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>577568</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078538</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>105310351</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>577578</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078460</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>105310352</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>577648</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078433</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>105310353</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>577622</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078434</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>119871836</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>577614</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078416</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>119871885</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>577588</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7078435</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133340413</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>577600</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7078399</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>102368367</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7078541</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>102368381</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>577351</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7078685</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>102368383</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>577366</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7078701</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>113361370</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tågsjötorp (Backe), Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>577440</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7078556</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-07-08</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-07-08</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133642794</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>577380</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7078565</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133642938</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>577389</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7078551</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>102368070</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Backe (63.8258, 16.5762), Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>577569</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7078560</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-07-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>102862723</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>577554</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7078567</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>102862765</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>577539</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7078588</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>102862799</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tägsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>577532</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7078587</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133378044</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>577359</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7078691</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133660017</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7078549</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368365</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113360892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870350</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871262</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871920</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872658</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870519</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368361</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870410</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871879</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873251</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368373</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368374</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368375</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368376</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368377</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368378</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368381</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2907,6 +3022,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368383</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361370</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871466</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871910</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871949</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872160</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132083264</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133642794</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133642938</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3792,6 +3952,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288904</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3893,6 +4058,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288957</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3994,6 +4164,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361143</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4095,6 +4270,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361358</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4192,6 +4372,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871553</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4289,6 +4474,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873378</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4386,6 +4576,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873387</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4483,6 +4678,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873511</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4580,6 +4780,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340463</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4677,6 +4882,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873574</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4789,6 +4999,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086547</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4901,6 +5116,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086668</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5013,6 +5233,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086694</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5125,6 +5350,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086911</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5237,6 +5467,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086988</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5353,6 +5588,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087060</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5465,6 +5705,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087340</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5577,6 +5822,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087456</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5689,6 +5939,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087499</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5801,6 +6056,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087575</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133675585</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5995,6 +6260,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368366</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6100,6 +6370,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873589</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6197,6 +6472,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128716003</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6298,6 +6578,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132084029</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6395,6 +6680,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368384</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6513,6 +6803,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368070</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6631,6 +6926,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368098</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6754,6 +7054,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368143</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6868,6 +7173,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368181</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6982,6 +7292,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368234</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7088,6 +7403,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368371</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7194,6 +7514,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368372</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7304,6 +7629,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102862533</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7418,6 +7748,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102862723</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7532,6 +7867,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102862765</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7646,6 +7986,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102862799</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7756,6 +8101,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102862973</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7858,6 +8208,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310351</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7960,6 +8315,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310352</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8062,6 +8422,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310353</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8163,6 +8528,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871836</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8260,6 +8630,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871885</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8366,6 +8741,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340413</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8472,6 +8852,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133378044</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8578,6 +8963,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133660017</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8675,6 +9065,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8772,8 +9167,94 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ80"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6586,45 +6586,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102368384</v>
+        <v>135642628</v>
       </c>
       <c r="B58" t="n">
-        <v>99035</v>
+        <v>58141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577494</v>
+        <v>577353</v>
       </c>
       <c r="R58" t="n">
-        <v>7078469</v>
+        <v>7078642</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6671,85 +6671,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368384</t>
+          <t>https://artportalen.se/Sighting/135642628</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102368070</v>
+        <v>102368384</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Backe (63.8258, 16.5762), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577569</v>
+        <v>577494</v>
       </c>
       <c r="R59" t="n">
-        <v>7078560</v>
+        <v>7078469</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6773,12 +6753,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6787,31 +6767,30 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac, Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368070</t>
+          <t>https://artportalen.se/Sighting/102368384</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102368098</v>
+        <v>102368070</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -6862,14 +6841,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Backe (63.8256, 16.5761), Ång</t>
+          <t>Backe (63.8258, 16.5762), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577565</v>
+        <v>577569</v>
       </c>
       <c r="R60" t="n">
-        <v>7078538</v>
+        <v>7078560</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6928,13 +6907,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368098</t>
+          <t>https://artportalen.se/Sighting/102368070</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102368143</v>
+        <v>102368098</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -6964,7 +6943,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6985,14 +6964,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Backe (63.8246, 16.5768), Ång</t>
+          <t>Backe (63.8256, 16.5761), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577602</v>
+        <v>577565</v>
       </c>
       <c r="R61" t="n">
-        <v>7078427</v>
+        <v>7078538</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7019,17 +6998,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7056,13 +7030,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368143</t>
+          <t>https://artportalen.se/Sighting/102368098</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102368181</v>
+        <v>102368143</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7092,7 +7066,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7106,17 +7080,21 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (63.8246, 16.5768), Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577673</v>
+        <v>577602</v>
       </c>
       <c r="R62" t="n">
-        <v>7078406</v>
+        <v>7078427</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7151,6 +7129,11 @@
           <t>2022-07-19</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7164,24 +7147,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368181</t>
+          <t>https://artportalen.se/Sighting/102368143</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102368234</v>
+        <v>102368181</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7232,10 +7215,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577675</v>
+        <v>577673</v>
       </c>
       <c r="R63" t="n">
-        <v>7078447</v>
+        <v>7078406</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,13 +7277,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368234</t>
+          <t>https://artportalen.se/Sighting/102368181</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102368371</v>
+        <v>102368234</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7330,26 +7313,34 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577648</v>
+        <v>577675</v>
       </c>
       <c r="R64" t="n">
-        <v>7078453</v>
+        <v>7078447</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7373,12 +7364,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7394,24 +7385,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368371</t>
+          <t>https://artportalen.se/Sighting/102368234</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102368372</v>
+        <v>102368371</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7441,7 +7432,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -7454,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577645</v>
+        <v>577648</v>
       </c>
       <c r="R65" t="n">
-        <v>7078483</v>
+        <v>7078453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7516,13 +7507,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368372</t>
+          <t>https://artportalen.se/Sighting/102368371</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102862533</v>
+        <v>102368372</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7550,17 +7541,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -7569,13 +7556,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577613</v>
+        <v>577645</v>
       </c>
       <c r="R66" t="n">
-        <v>7078506</v>
+        <v>7078483</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7599,12 +7586,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7620,24 +7607,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862533</t>
+          <t>https://artportalen.se/Sighting/102368372</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102862723</v>
+        <v>102862533</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7677,24 +7664,20 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577554</v>
+        <v>577613</v>
       </c>
       <c r="R67" t="n">
-        <v>7078567</v>
+        <v>7078506</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7750,13 +7733,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862723</t>
+          <t>https://artportalen.se/Sighting/102862533</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102862765</v>
+        <v>102862723</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7807,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577539</v>
+        <v>577554</v>
       </c>
       <c r="R68" t="n">
-        <v>7078588</v>
+        <v>7078567</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7869,13 +7852,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862765</t>
+          <t>https://artportalen.se/Sighting/102862723</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102862799</v>
+        <v>102862765</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7922,14 +7905,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tägsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577532</v>
+        <v>577539</v>
       </c>
       <c r="R69" t="n">
-        <v>7078587</v>
+        <v>7078588</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7988,13 +7971,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862799</t>
+          <t>https://artportalen.se/Sighting/102862765</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102862973</v>
+        <v>102862799</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8034,17 +8017,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tägsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577568</v>
+        <v>577532</v>
       </c>
       <c r="R70" t="n">
-        <v>7078538</v>
+        <v>7078587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,13 +8090,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862973</t>
+          <t>https://artportalen.se/Sighting/102862799</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105310351</v>
+        <v>102862973</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8138,19 +8125,31 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577578</v>
+        <v>577568</v>
       </c>
       <c r="R71" t="n">
-        <v>7078460</v>
+        <v>7078538</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8174,12 +8173,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8188,35 +8187,31 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310351</t>
+          <t>https://artportalen.se/Sighting/102862973</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105310352</v>
+        <v>105310351</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8251,10 +8246,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577648</v>
+        <v>577578</v>
       </c>
       <c r="R72" t="n">
-        <v>7078433</v>
+        <v>7078460</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8317,13 +8312,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310352</t>
+          <t>https://artportalen.se/Sighting/105310351</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>105310353</v>
+        <v>105310352</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8358,10 +8353,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577622</v>
+        <v>577648</v>
       </c>
       <c r="R73" t="n">
-        <v>7078434</v>
+        <v>7078433</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8424,13 +8419,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310353</t>
+          <t>https://artportalen.se/Sighting/105310352</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119871836</v>
+        <v>105310353</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8458,24 +8453,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577614</v>
+        <v>577622</v>
       </c>
       <c r="R74" t="n">
-        <v>7078416</v>
+        <v>7078434</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,12 +8490,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8515,28 +8506,33 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871836</t>
+          <t>https://artportalen.se/Sighting/105310353</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119871885</v>
+        <v>119871836</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8564,20 +8560,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R75" t="n">
-        <v>7078435</v>
+        <v>7078416</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8621,27 +8621,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871885</t>
+          <t>https://artportalen.se/Sighting/119871836</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133340413</v>
+        <v>119871885</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8666,29 +8666,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577600</v>
+        <v>577588</v>
       </c>
       <c r="R76" t="n">
-        <v>7078399</v>
+        <v>7078435</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,12 +8703,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8743,13 +8734,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340413</t>
+          <t>https://artportalen.se/Sighting/119871885</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133378044</v>
+        <v>133340413</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -8779,7 +8770,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8789,17 +8780,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577359</v>
+        <v>577600</v>
       </c>
       <c r="R77" t="n">
-        <v>7078691</v>
+        <v>7078399</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8823,12 +8814,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8854,13 +8845,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133378044</t>
+          <t>https://artportalen.se/Sighting/133340413</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133660017</v>
+        <v>133378044</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -8890,7 +8881,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8904,13 +8895,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577392</v>
+        <v>577359</v>
       </c>
       <c r="R78" t="n">
-        <v>7078549</v>
+        <v>7078691</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8934,12 +8925,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8965,54 +8956,63 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133660017</t>
+          <t>https://artportalen.se/Sighting/133378044</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102368367</v>
+        <v>133660017</v>
       </c>
       <c r="B79" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
         <v>577392</v>
       </c>
       <c r="R79" t="n">
-        <v>7078541</v>
+        <v>7078549</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9056,65 +9056,74 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/133660017</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102368369</v>
+        <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99140</v>
+        <v>99242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577333</v>
+        <v>577401</v>
       </c>
       <c r="R80" t="n">
-        <v>7078674</v>
+        <v>7078525</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9138,12 +9147,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,16 +9167,220 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644617</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>102368367</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7078541</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9254,6 +9467,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ80"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6586,45 +6586,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102368384</v>
+        <v>135642628</v>
       </c>
       <c r="B58" t="n">
-        <v>99035</v>
+        <v>58141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577494</v>
+        <v>577353</v>
       </c>
       <c r="R58" t="n">
-        <v>7078469</v>
+        <v>7078642</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6671,85 +6671,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368384</t>
+          <t>https://artportalen.se/Sighting/135642628</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102368070</v>
+        <v>102368384</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Backe (63.8258, 16.5762), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577569</v>
+        <v>577494</v>
       </c>
       <c r="R59" t="n">
-        <v>7078560</v>
+        <v>7078469</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6773,12 +6753,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6787,31 +6767,30 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac, Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368070</t>
+          <t>https://artportalen.se/Sighting/102368384</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102368098</v>
+        <v>102368070</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -6862,14 +6841,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Backe (63.8256, 16.5761), Ång</t>
+          <t>Backe (63.8258, 16.5762), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577565</v>
+        <v>577569</v>
       </c>
       <c r="R60" t="n">
-        <v>7078538</v>
+        <v>7078560</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6928,13 +6907,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368098</t>
+          <t>https://artportalen.se/Sighting/102368070</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102368143</v>
+        <v>102368098</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -6964,7 +6943,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6985,14 +6964,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Backe (63.8246, 16.5768), Ång</t>
+          <t>Backe (63.8256, 16.5761), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577602</v>
+        <v>577565</v>
       </c>
       <c r="R61" t="n">
-        <v>7078427</v>
+        <v>7078538</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7019,17 +6998,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7056,13 +7030,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368143</t>
+          <t>https://artportalen.se/Sighting/102368098</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102368181</v>
+        <v>102368143</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7092,7 +7066,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7106,17 +7080,21 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (63.8246, 16.5768), Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577673</v>
+        <v>577602</v>
       </c>
       <c r="R62" t="n">
-        <v>7078406</v>
+        <v>7078427</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7151,6 +7129,11 @@
           <t>2022-07-19</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7164,24 +7147,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368181</t>
+          <t>https://artportalen.se/Sighting/102368143</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102368234</v>
+        <v>102368181</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7232,10 +7215,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577675</v>
+        <v>577673</v>
       </c>
       <c r="R63" t="n">
-        <v>7078447</v>
+        <v>7078406</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,13 +7277,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368234</t>
+          <t>https://artportalen.se/Sighting/102368181</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102368371</v>
+        <v>102368234</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7330,26 +7313,34 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577648</v>
+        <v>577675</v>
       </c>
       <c r="R64" t="n">
-        <v>7078453</v>
+        <v>7078447</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7373,12 +7364,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7394,24 +7385,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368371</t>
+          <t>https://artportalen.se/Sighting/102368234</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102368372</v>
+        <v>102368371</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7441,7 +7432,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -7454,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577645</v>
+        <v>577648</v>
       </c>
       <c r="R65" t="n">
-        <v>7078483</v>
+        <v>7078453</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7516,13 +7507,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368372</t>
+          <t>https://artportalen.se/Sighting/102368371</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102862533</v>
+        <v>102368372</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7550,17 +7541,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -7569,13 +7556,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577613</v>
+        <v>577645</v>
       </c>
       <c r="R66" t="n">
-        <v>7078506</v>
+        <v>7078483</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7599,12 +7586,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7620,24 +7607,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862533</t>
+          <t>https://artportalen.se/Sighting/102368372</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102862723</v>
+        <v>102862533</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7677,24 +7664,20 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577554</v>
+        <v>577613</v>
       </c>
       <c r="R67" t="n">
-        <v>7078567</v>
+        <v>7078506</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7750,13 +7733,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862723</t>
+          <t>https://artportalen.se/Sighting/102862533</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102862765</v>
+        <v>102862723</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7807,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577539</v>
+        <v>577554</v>
       </c>
       <c r="R68" t="n">
-        <v>7078588</v>
+        <v>7078567</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7869,13 +7852,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862765</t>
+          <t>https://artportalen.se/Sighting/102862723</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102862799</v>
+        <v>102862765</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7922,14 +7905,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tägsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577532</v>
+        <v>577539</v>
       </c>
       <c r="R69" t="n">
-        <v>7078587</v>
+        <v>7078588</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7988,13 +7971,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862799</t>
+          <t>https://artportalen.se/Sighting/102862765</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102862973</v>
+        <v>102862799</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8034,17 +8017,21 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tägsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577568</v>
+        <v>577532</v>
       </c>
       <c r="R70" t="n">
-        <v>7078538</v>
+        <v>7078587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8103,13 +8090,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102862973</t>
+          <t>https://artportalen.se/Sighting/102862799</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105310351</v>
+        <v>102862973</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8138,19 +8125,31 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577578</v>
+        <v>577568</v>
       </c>
       <c r="R71" t="n">
-        <v>7078460</v>
+        <v>7078538</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8174,12 +8173,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8188,35 +8187,31 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310351</t>
+          <t>https://artportalen.se/Sighting/102862973</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>105310352</v>
+        <v>105310351</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8251,10 +8246,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577648</v>
+        <v>577578</v>
       </c>
       <c r="R72" t="n">
-        <v>7078433</v>
+        <v>7078460</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8317,13 +8312,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310352</t>
+          <t>https://artportalen.se/Sighting/105310351</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>105310353</v>
+        <v>105310352</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8358,10 +8353,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577622</v>
+        <v>577648</v>
       </c>
       <c r="R73" t="n">
-        <v>7078434</v>
+        <v>7078433</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8424,13 +8419,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310353</t>
+          <t>https://artportalen.se/Sighting/105310352</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119871836</v>
+        <v>105310353</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8458,24 +8453,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577614</v>
+        <v>577622</v>
       </c>
       <c r="R74" t="n">
-        <v>7078416</v>
+        <v>7078434</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8499,12 +8490,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8515,28 +8506,33 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871836</t>
+          <t>https://artportalen.se/Sighting/105310353</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119871885</v>
+        <v>119871836</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8564,20 +8560,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R75" t="n">
-        <v>7078435</v>
+        <v>7078416</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8621,27 +8621,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871885</t>
+          <t>https://artportalen.se/Sighting/119871836</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133340413</v>
+        <v>119871885</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8666,29 +8666,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577600</v>
+        <v>577588</v>
       </c>
       <c r="R76" t="n">
-        <v>7078399</v>
+        <v>7078435</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,12 +8703,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8743,13 +8734,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340413</t>
+          <t>https://artportalen.se/Sighting/119871885</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133378044</v>
+        <v>133340413</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -8779,7 +8770,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8789,17 +8780,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577359</v>
+        <v>577600</v>
       </c>
       <c r="R77" t="n">
-        <v>7078691</v>
+        <v>7078399</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8823,12 +8814,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8854,13 +8845,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133378044</t>
+          <t>https://artportalen.se/Sighting/133340413</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133660017</v>
+        <v>133378044</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -8890,7 +8881,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8904,13 +8895,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577392</v>
+        <v>577359</v>
       </c>
       <c r="R78" t="n">
-        <v>7078549</v>
+        <v>7078691</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8934,12 +8925,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8965,54 +8956,63 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133660017</t>
+          <t>https://artportalen.se/Sighting/133378044</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102368367</v>
+        <v>133660017</v>
       </c>
       <c r="B79" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
         <v>577392</v>
       </c>
       <c r="R79" t="n">
-        <v>7078541</v>
+        <v>7078549</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9056,65 +9056,74 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/133660017</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102368369</v>
+        <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99140</v>
+        <v>99274</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577333</v>
+        <v>577401</v>
       </c>
       <c r="R80" t="n">
-        <v>7078674</v>
+        <v>7078525</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9138,12 +9147,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9158,16 +9167,220 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644617</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>102368367</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7078541</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9254,6 +9467,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9184,45 +9184,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102368367</v>
+        <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99140</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577392</v>
+        <v>577347</v>
       </c>
       <c r="R81" t="n">
-        <v>7078541</v>
+        <v>7078675</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9249,12 +9258,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9269,24 +9278,24 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/135951509</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>102368369</v>
+        <v>102368367</v>
       </c>
       <c r="B82" t="n">
         <v>99140</v>
@@ -9321,10 +9330,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577333</v>
+        <v>577392</v>
       </c>
       <c r="R82" t="n">
-        <v>7078674</v>
+        <v>7078541</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9381,6 +9390,108 @@
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9469,6 +9580,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -6589,7 +6589,7 @@
         <v>135642628</v>
       </c>
       <c r="B58" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -6589,7 +6589,7 @@
         <v>135642628</v>
       </c>
       <c r="B58" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -6589,7 +6589,7 @@
         <v>135642628</v>
       </c>
       <c r="B58" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135644617</v>
       </c>
       <c r="B80" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 26655-2022 artfynd.xlsx
+++ b/artfynd/A 26655-2022 artfynd.xlsx
@@ -9187,7 +9187,7 @@
         <v>135951509</v>
       </c>
       <c r="B81" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
